--- a/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-clinical-diagnosis-category.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-clinical-diagnosis-category.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T13:39:17+00:00</t>
+    <t>2026-08-28T13:49:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-clinical-diagnosis-category.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-clinical-diagnosis-category.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T13:49:20+00:00</t>
+    <t>2026-08-28T14:00:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-clinical-diagnosis-category.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-clinical-diagnosis-category.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T14:00:29+00:00</t>
+    <t>2026-08-31T13:41:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-clinical-diagnosis-category.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-clinical-diagnosis-category.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T13:41:24+00:00</t>
+    <t>2026-09-02T03:14:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-clinical-diagnosis-category.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-clinical-diagnosis-category.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T03:14:53+00:00</t>
+    <t>2026-09-02T03:38:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-clinical-diagnosis-category.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-clinical-diagnosis-category.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T03:38:58+00:00</t>
+    <t>2026-09-02T04:00:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-clinical-diagnosis-category.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-clinical-diagnosis-category.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T04:00:55+00:00</t>
+    <t>2026-09-02T06:41:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-clinical-diagnosis-category.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-clinical-diagnosis-category.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T06:41:45+00:00</t>
+    <t>2026-09-02T06:59:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-clinical-diagnosis-category.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-clinical-diagnosis-category.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T06:59:28+00:00</t>
+    <t>2026-09-02T09:29:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-clinical-diagnosis-category.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-clinical-diagnosis-category.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T09:29:03+00:00</t>
+    <t>2026-09-02T14:14:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-clinical-diagnosis-category.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-clinical-diagnosis-category.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T14:14:40+00:00</t>
+    <t>2026-09-02T14:33:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-clinical-diagnosis-category.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-clinical-diagnosis-category.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T14:33:43+00:00</t>
+    <t>2026-09-02T15:16:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-clinical-diagnosis-category.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-clinical-diagnosis-category.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T15:16:54+00:00</t>
+    <t>2026-09-02T16:13:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-clinical-diagnosis-category.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-clinical-diagnosis-category.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T16:13:05+00:00</t>
+    <t>2026-09-02T16:35:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-clinical-diagnosis-category.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-clinical-diagnosis-category.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T16:35:11+00:00</t>
+    <t>2026-09-02T16:52:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-clinical-diagnosis-category.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-clinical-diagnosis-category.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="43">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T16:52:58+00:00</t>
+    <t>2026-09-02T17:07:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -105,7 +105,7 @@
     <t>Diagnosis</t>
   </si>
   <si>
-    <t>363358000</t>
+    <t>404684003</t>
   </si>
   <si>
     <t>Clinical finding</t>
@@ -117,6 +117,12 @@
     <t>Disease</t>
   </si>
   <si>
+    <t>66091009</t>
+  </si>
+  <si>
+    <t>Congenital disease</t>
+  </si>
+  <si>
     <t>609328004</t>
   </si>
   <si>
@@ -127,24 +133,6 @@
   </si>
   <si>
     <t>Autoimmune disease</t>
-  </si>
-  <si>
-    <t>47367009</t>
-  </si>
-  <si>
-    <t>Syndrome</t>
-  </si>
-  <si>
-    <t>381406004</t>
-  </si>
-  <si>
-    <t>Congenital disorder</t>
-  </si>
-  <si>
-    <t>84757009</t>
-  </si>
-  <si>
-    <t>Rare disease</t>
   </si>
   <si>
     <t/>
@@ -415,7 +403,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -483,31 +471,15 @@
         <v>40</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B9" t="s" s="2">
         <v>42</v>
-      </c>
-      <c r="B9" t="s" s="2">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="s" s="2">
-        <v>44</v>
-      </c>
-      <c r="B10" t="s" s="2">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="s" s="2">
-        <v>45</v>
-      </c>
-      <c r="B11" t="s" s="2">
-        <v>46</v>
       </c>
     </row>
   </sheetData>

--- a/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-clinical-diagnosis-category.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-clinical-diagnosis-category.xlsx
@@ -42,13 +42,13 @@
     <t>Title</t>
   </si>
   <si>
-    <t>MII VS SE Clinical Diagnosis Category</t>
+    <t>MII VS SE Clinical Diagnosis Category (retired)</t>
   </si>
   <si>
     <t>Status</t>
   </si>
   <si>
-    <t>active</t>
+    <t>retired</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T17:07:58+00:00</t>
+    <t>2026-09-02T17:34:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Value set for categorizing clinical diagnoses of rare diseases</t>
+    <t>RETIRED. Nicht verwenden. Das ValueSet war zur Kategorisierung klinischer Diagnosen gedacht, beantwortet aber die falsche Frage: Condition.category bezeichnet in FHIR die Rolle der Condition im Datensatz, nicht die Art der Krankheit. Die Krankheitsart gehoert in Condition.code.</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-clinical-diagnosis-category.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-clinical-diagnosis-category.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T17:34:23+00:00</t>
+    <t>2026-09-02T17:52:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-clinical-diagnosis-category.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-clinical-diagnosis-category.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T17:52:03+00:00</t>
+    <t>2026-09-02T18:22:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-clinical-diagnosis-category.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-clinical-diagnosis-category.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T18:22:51+00:00</t>
+    <t>2026-09-03T06:59:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-clinical-diagnosis-category.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-clinical-diagnosis-category.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot</t>
+    <t>2027.0.0-ballot.rc1</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T06:59:35+00:00</t>
+    <t>2026-09-03T07:17:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-clinical-diagnosis-category.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-clinical-diagnosis-category.xlsx
@@ -36,7 +36,7 @@
     <t>Name</t>
   </si>
   <si>
-    <t>ClinicalDiagnosisCategoryVS</t>
+    <t>MII_VS_Seltene_ClinicalDiagnosisCategory</t>
   </si>
   <si>
     <t>Title</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T07:17:59+00:00</t>
+    <t>2026-09-03T07:33:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-clinical-diagnosis-category.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-clinical-diagnosis-category.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T07:33:22+00:00</t>
+    <t>2026-09-03T09:08:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-clinical-diagnosis-category.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-clinical-diagnosis-category.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T09:08:22+00:00</t>
+    <t>2026-09-03T09:27:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-clinical-diagnosis-category.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-clinical-diagnosis-category.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T09:27:13+00:00</t>
+    <t>2026-09-03T09:44:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-clinical-diagnosis-category.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-clinical-diagnosis-category.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T09:44:41+00:00</t>
+    <t>2026-09-03T10:23:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
